--- a/donnees.xlsx
+++ b/donnees.xlsx
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>a65</t>
+          <t>machoire blanche</t>
         </is>
       </c>
     </row>
